--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/StarPicture_评分表.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/StarPicture_评分表.xlsx
@@ -1560,13 +1560,13 @@
         </is>
       </c>
       <c r="I3" s="40" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J3" s="40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3" s="40" t="n">
         <v>2</v>
@@ -1605,7 +1605,7 @@
       <c r="W3" s="29" t="n"/>
       <c r="X3" s="42" t="inlineStr">
         <is>
-          <t>朱远亮 实际 28 条（功能+性能+接口+安全）</t>
+          <t>朱远亮 实际 30 条</t>
         </is>
       </c>
     </row>
@@ -1632,16 +1632,16 @@
         </is>
       </c>
       <c r="I4" s="40" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="J4" s="40" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="40" t="n">
         <v>3</v>
-      </c>
-      <c r="L4" s="40" t="n">
-        <v>4</v>
       </c>
       <c r="M4" s="40" t="n">
         <v>0</v>
@@ -1677,7 +1677,7 @@
       <c r="W4" s="29" t="n"/>
       <c r="X4" s="42" t="inlineStr">
         <is>
-          <t>李冠燃 实际 28 条（功能+性能+接口+安全）</t>
+          <t>李冠燃 实际 45 条</t>
         </is>
       </c>
     </row>
@@ -1704,13 +1704,13 @@
         </is>
       </c>
       <c r="I5" s="40" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J5" s="40" t="n">
         <v>2</v>
       </c>
       <c r="K5" s="40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" s="40" t="n">
         <v>2</v>
@@ -1749,7 +1749,7 @@
       <c r="W5" s="29" t="n"/>
       <c r="X5" s="42" t="inlineStr">
         <is>
-          <t>李坤纬 实际 29 条（功能+性能+接口+安全）</t>
+          <t>李坤纬 实际 47 条</t>
         </is>
       </c>
     </row>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="I6" s="40" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J6" s="40" t="n">
         <v>2</v>
       </c>
       <c r="K6" s="40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" s="40" t="n">
         <v>3</v>
@@ -1821,7 +1821,7 @@
       <c r="W6" s="29" t="n"/>
       <c r="X6" s="42" t="inlineStr">
         <is>
-          <t>林景彬 实际 28 条（功能+性能+接口+安全）</t>
+          <t>林景彬 实际 24 条</t>
         </is>
       </c>
     </row>
@@ -1932,8 +1932,8 @@
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="G1:G2"/>
+    <mergeCell ref="V1:V2"/>
     <mergeCell ref="R1:R2"/>
-    <mergeCell ref="V1:V2"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="D1:F1"/>

--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/StarPicture_评分表.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/StarPicture_评分表.xlsx
@@ -1560,16 +1560,16 @@
         </is>
       </c>
       <c r="I3" s="40" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J3" s="40" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K3" s="40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="40" t="n">
         <v>0</v>
@@ -1605,7 +1605,7 @@
       <c r="W3" s="29" t="n"/>
       <c r="X3" s="42" t="inlineStr">
         <is>
-          <t>朱远亮 实际 30 条</t>
+          <t>朱远亮 实际 31 条（功能+性能+接口+安全）</t>
         </is>
       </c>
     </row>
@@ -1903,6 +1903,9 @@
       <c r="W9" s="29" t="n"/>
       <c r="X9" s="42" t="n"/>
     </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
     <row r="13">
       <c r="G13" s="40" t="n"/>
       <c r="H13" s="33" t="inlineStr">

--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/StarPicture_评分表.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/StarPicture_评分表.xlsx
@@ -1554,19 +1554,17 @@
         <f>IF(D3="优秀",14,IF(D3="中上",12,IF(D3="中等",10,IF(D3="中下",8,6))))+IF(E3="优秀",13,IF(E3="中上",11,IF(E3="中等",9,IF(E3="中下",7,5))))+IF(F3="优秀",13,IF(F3="中上",12,IF(F3="中等",9,IF(F3="中下",7,5))))</f>
         <v/>
       </c>
-      <c r="H3" s="24" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
+      <c r="H3" s="24" t="n">
+        <v>11</v>
       </c>
       <c r="I3" s="40" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J3" s="40" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K3" s="40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L3" s="40" t="n">
         <v>0</v>
@@ -1605,7 +1603,7 @@
       <c r="W3" s="29" t="n"/>
       <c r="X3" s="42" t="inlineStr">
         <is>
-          <t>朱远亮 实际 31 条（功能+性能+接口+安全）</t>
+          <t>朱远亮 实际 26 条（功能11+性能6+接口3+安全6）</t>
         </is>
       </c>
     </row>

--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/StarPicture_评分表.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/StarPicture_评分表.xlsx
@@ -1600,7 +1600,11 @@
         <f>IF(U3="优秀",10,IF(U3="中上",8,IF(U3="中等",6,IF(U3="中下",5,4))))</f>
         <v/>
       </c>
-      <c r="W3" s="29" t="n"/>
+      <c r="W3" s="29" t="inlineStr">
+        <is>
+          <t>朱远亮 实际 31 条（功能+性能+接口+安全）</t>
+        </is>
+      </c>
       <c r="X3" s="42" t="inlineStr">
         <is>
           <t>朱远亮 实际 26 条（功能11+性能6+接口3+安全6）</t>
@@ -1672,7 +1676,11 @@
         <f>IF(U4="优秀",10,IF(U4="中上",8,IF(U4="中等",6,IF(U4="中下",5,4))))</f>
         <v/>
       </c>
-      <c r="W4" s="29" t="n"/>
+      <c r="W4" s="29" t="inlineStr">
+        <is>
+          <t>李冠燃 实际 45 条（功能+性能+接口+安全）</t>
+        </is>
+      </c>
       <c r="X4" s="42" t="inlineStr">
         <is>
           <t>李冠燃 实际 45 条</t>
@@ -1744,7 +1752,11 @@
         <f>IF(U5="优秀",10,IF(U5="中上",8,IF(U5="中等",6,IF(U5="中下",5,4))))</f>
         <v/>
       </c>
-      <c r="W5" s="29" t="n"/>
+      <c r="W5" s="29" t="inlineStr">
+        <is>
+          <t>李坤纬 实际 34 条（功能+性能+接口+安全）</t>
+        </is>
+      </c>
       <c r="X5" s="42" t="inlineStr">
         <is>
           <t>李坤纬 实际 47 条</t>
@@ -1816,7 +1828,11 @@
         <f>IF(U6="优秀",10,IF(U6="中上",8,IF(U6="中等",6,IF(U6="中下",5,4))))</f>
         <v/>
       </c>
-      <c r="W6" s="29" t="n"/>
+      <c r="W6" s="29" t="inlineStr">
+        <is>
+          <t>林景彬 实际 25 条（功能+性能+接口+安全）</t>
+        </is>
+      </c>
       <c r="X6" s="42" t="inlineStr">
         <is>
           <t>林景彬 实际 24 条</t>

--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/StarPicture_评分表.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/StarPicture_评分表.xlsx
@@ -1555,16 +1555,16 @@
         <v/>
       </c>
       <c r="H3" s="24" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="I3" s="40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J3" s="40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3" s="40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L3" s="40" t="n">
         <v>0</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="X3" s="42" t="inlineStr">
         <is>
-          <t>朱远亮 实际 26 条（功能11+性能6+接口3+安全6）</t>
+          <t>朱远亮 实际 31 条（功能29+性能1+接口1+安全0）</t>
         </is>
       </c>
     </row>
